--- a/_Learn/Yi.Studio.event/latest.xlsx
+++ b/_Learn/Yi.Studio.event/latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YiSolutions\_Learn\Yi.Studio.event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{601067AD-115D-468C-8035-6CC65F3A1731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64AFF989-2A66-4280-BB15-8B049EEB446D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0FB26A-90DE-4D19-99B5-A0F2311A7EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="84">
   <si>
     <t>分享连接</t>
   </si>
@@ -1196,21 +1193,6 @@
 5BC92707F821366B1FAF6D8C1DFA36C85E1249134963A0E1FE5AA4469D2D8BCB</t>
   </si>
   <si>
-    <t xml:space="preserve">    2025 / 10</t>
-  </si>
-  <si>
-    <t>25S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  封装事件代号：25S4（25 = 2025 年、S = 季度，4 = 第 4 季度），此系统由 Yi's Solutions v1.0.1.7 自动驾驶仪封装，前往学习或自定义封装：https://fengyi.tel/solutions，https://github.com/ilikeyi/solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Package event code: 25S4 (25 = 2025, S = quarter, 4 = Q4), this system is packaged by Yi's Solutions v1.0.1.7 autopilot, go to learn or customize the package: https://fengyi.tel/solutions, https://github.com/ilikeyi/solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Windows 11 25H2 26200.6725</t>
-  </si>
-  <si>
     <t>mul_Yi_Windows_11_25H2_With_Office_365_x64_2l1_19in1_f1we6gff_october_2025.iso
 DC1D577366B4A77162496B4932AC558E1006DAAF36D7D6BAB237C75659A2D3BA</t>
   </si>
@@ -1221,6 +1203,33 @@
   <si>
     <t>mul_Yi_Windows_11_25H2_x64_2l1_19in1_i9aafr0y_october_2025.iso
 E453C0725D3F54901E0F86BE3A4A49E29954A49BD1E50AA8F5464D91B3FD9586</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_24H2_x64_2l1_19in1_f2got7ei_november_2025.iso
+7C4DB229543BFA6BF3E65B1F29C2E8A85C1F2778827C55803221FDA39D45B474</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_24H2_With_Office_2024_x64_2l1_19in1_05xisefy_november_2025.iso
+0F9F945798CEBCAC70F8854D50E5B7333A8F72361B1E3C281D8732055428A079</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_24H2_With_Office_365_x64_2l1_19in1_m3l7sjp7_november_2025.iso
+1ED18D7ECF7BDB2C7D8E84FC6CC8502473AB8347335B6826A3B1AC502E9A8911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Windows 11 25H2 26200.7296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2025 / 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Package event code: 25S4 ( 25 = 2025, S = quarter, 4 = Q4, N = November ), this system is packaged by Yi's Solutions v1.0.1.8 autopilot, go to learn or customize the package: https://fengyi.tel/solutions, https://github.com/ilikeyi/solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  封装事件代号：25S4N（ 25 = 2025 年、S = 季度，4 = 第 4 季度，N = 11 月 ），此系统由 Yi's Solutions v1.0.1.8 自动驾驶仪封装，前往学习或自定义封装：https://fengyi.tel/solutions，https://github.com/ilikeyi/solutions</t>
+  </si>
+  <si>
+    <t>25S4N</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1373,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1419,12 +1428,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1524,7 +1527,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1647,31 +1650,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="10" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1711,7 +1699,85 @@
     <cellStyle name="Total" xfId="4" builtinId="25" customBuiltin="1"/>
     <cellStyle name="z Hidden Text" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1992,17 +2058,17 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Home Inventory" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Home Inventory" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="lastColumn" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
-      <tableStyleElement type="firstTotalCell" dxfId="15"/>
+      <tableStyleElement type="wholeTable" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="lastColumn" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
+      <tableStyleElement type="firstTotalCell" dxfId="21"/>
     </tableStyle>
     <tableStyle name="Home Inventory Slicer" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="wholeTable" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2539,7 +2605,7 @@
     <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9"/>
       <c r="C3" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -2551,13 +2617,13 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="40"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
       <c r="I4" s="17"/>
       <c r="J4" s="18"/>
     </row>
@@ -2566,14 +2632,14 @@
       <c r="C5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="47"/>
+      <c r="E5" s="42"/>
       <c r="F5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="19" t="s">
         <v>70</v>
       </c>
       <c r="H5" s="19" t="s">
@@ -2605,7 +2671,7 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="43"/>
+      <c r="G7" s="15"/>
       <c r="H7" s="34"/>
       <c r="I7" s="34"/>
       <c r="J7" s="34"/>
@@ -2613,19 +2679,19 @@
     <row r="8" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="20"/>
       <c r="C8" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="39" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>42</v>
@@ -2645,7 +2711,7 @@
       <c r="D9" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="39" t="s">
         <v>72</v>
       </c>
       <c r="F9" s="20" t="s">
@@ -2692,7 +2758,7 @@
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="43"/>
+      <c r="G12" s="15"/>
       <c r="H12" s="34"/>
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
@@ -2701,19 +2767,19 @@
     <row r="13" spans="1:11" s="15" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="20"/>
       <c r="C13" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="39" t="s">
         <v>58</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>42</v>
@@ -2733,7 +2799,7 @@
       <c r="D14" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="39" t="s">
         <v>71</v>
       </c>
       <c r="F14" s="20" t="s">
@@ -2787,19 +2853,19 @@
     <row r="18" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="20"/>
       <c r="C18" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="39" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>42</v>
@@ -2819,7 +2885,7 @@
       <c r="D19" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="39" t="s">
         <v>67</v>
       </c>
       <c r="F19" s="20" t="s">
@@ -2866,7 +2932,7 @@
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
       <c r="F22" s="15"/>
-      <c r="G22" s="43"/>
+      <c r="G22" s="15"/>
       <c r="H22" s="34"/>
       <c r="I22" s="34"/>
       <c r="J22" s="34"/>
@@ -2901,19 +2967,19 @@
     <row r="25" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="39" t="s">
         <v>56</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>42</v>
@@ -2931,14 +2997,14 @@
       <c r="D26" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="E26" s="39" t="s">
         <v>55</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>43</v>
@@ -2956,14 +3022,14 @@
       <c r="D27" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="39" t="s">
         <v>54</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>41</v>
@@ -2994,7 +3060,7 @@
       <c r="D29" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="39" t="s">
         <v>66</v>
       </c>
       <c r="F29" s="20" t="s">
@@ -3020,7 +3086,7 @@
       <c r="D30" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="39" t="s">
         <v>65</v>
       </c>
       <c r="F30" s="20" t="s">
@@ -3045,7 +3111,7 @@
       <c r="D31" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="42" t="s">
+      <c r="E31" s="39" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="20" t="s">
@@ -3099,19 +3165,19 @@
     <row r="35" spans="2:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="20"/>
       <c r="C35" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D35" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="42" t="s">
-        <v>80</v>
+      <c r="E35" s="39" t="s">
+        <v>76</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H35" s="22" t="s">
         <v>42</v>
@@ -3129,14 +3195,14 @@
       <c r="D36" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="42" t="s">
-        <v>79</v>
+      <c r="E36" s="39" t="s">
+        <v>77</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>43</v>
@@ -3154,14 +3220,14 @@
       <c r="D37" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="42" t="s">
+      <c r="E37" s="39" t="s">
         <v>78</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>41</v>
@@ -3192,7 +3258,7 @@
       <c r="D39" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="E39" s="39" t="s">
         <v>61</v>
       </c>
       <c r="F39" s="20" t="s">
@@ -3217,7 +3283,7 @@
       <c r="D40" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="39" t="s">
         <v>62</v>
       </c>
       <c r="F40" s="20" t="s">
@@ -3242,7 +3308,7 @@
       <c r="D41" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="42" t="s">
+      <c r="E41" s="39" t="s">
         <v>63</v>
       </c>
       <c r="F41" s="20" t="s">
@@ -3267,19 +3333,19 @@
       <c r="C43" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="D43" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="47"/>
+      <c r="E43" s="42"/>
       <c r="F43" s="19"/>
-      <c r="G43" s="44"/>
+      <c r="G43" s="19"/>
       <c r="H43" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="47"/>
+      <c r="J43" s="42"/>
     </row>
     <row r="44" spans="2:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="17"/>
@@ -3293,10 +3359,10 @@
       <c r="F44" s="36"/>
       <c r="G44" s="36"/>
       <c r="H44" s="35"/>
-      <c r="I44" s="46" t="s">
+      <c r="I44" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="46"/>
+      <c r="J44" s="41"/>
     </row>
     <row r="45" spans="2:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="18"/>
@@ -3310,8 +3376,8 @@
       <c r="F45" s="36"/>
       <c r="G45" s="36"/>
       <c r="H45" s="35"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="2:11" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3344,7 +3410,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E49" s="33"/>
       <c r="I49" s="15"/>
@@ -3601,52 +3667,62 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:J9">
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="18" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:J14">
-    <cfRule type="expression" dxfId="11" priority="8">
+  <conditionalFormatting sqref="C14:J14 C13:F13 H13:J13">
+    <cfRule type="expression" dxfId="17" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:J19">
-    <cfRule type="expression" dxfId="10" priority="6">
+  <conditionalFormatting sqref="C19:J19 C18:F18 H18:J18">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:J27">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:J31">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:J37">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:J41">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:J45">
-    <cfRule type="expression" dxfId="5" priority="56">
+    <cfRule type="expression" dxfId="11" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I39:J41 I8:J9 I13:J14 I18:J19 I25:J27 I35:J37 I29:J31">
-    <cfRule type="iconSet" priority="303">
+    <cfRule type="iconSet" priority="305">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
       </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3720,7 +3796,7 @@
     <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9"/>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -3732,33 +3808,33 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="40"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
       <c r="I4" s="17"/>
       <c r="J4" s="18"/>
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="19"/>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="39" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="19" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="19" t="s">
@@ -3797,19 +3873,19 @@
     <row r="8" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="20"/>
       <c r="C8" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="39" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>45</v>
@@ -3830,7 +3906,7 @@
       <c r="D9" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="39" t="s">
         <v>72</v>
       </c>
       <c r="F9" s="20" t="s">
@@ -3885,19 +3961,19 @@
     <row r="13" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="20"/>
       <c r="C13" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="39" t="s">
         <v>58</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>45</v>
@@ -3918,7 +3994,7 @@
       <c r="D14" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="39" t="s">
         <v>71</v>
       </c>
       <c r="F14" s="20" t="s">
@@ -3973,19 +4049,19 @@
     <row r="18" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="20"/>
       <c r="C18" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="39" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>45</v>
@@ -4006,7 +4082,7 @@
       <c r="D19" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="39" t="s">
         <v>67</v>
       </c>
       <c r="F19" s="20" t="s">
@@ -4093,19 +4169,19 @@
     <row r="25" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="42" t="s">
-        <v>56</v>
+      <c r="E25" s="39" t="s">
+        <v>76</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>45</v>
@@ -4124,14 +4200,14 @@
       <c r="D26" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="42" t="s">
-        <v>55</v>
+      <c r="E26" s="39" t="s">
+        <v>77</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>46</v>
@@ -4150,14 +4226,14 @@
       <c r="D27" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="42" t="s">
-        <v>54</v>
+      <c r="E27" s="39" t="s">
+        <v>78</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>44</v>
@@ -4190,7 +4266,7 @@
       <c r="D29" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="39" t="s">
         <v>66</v>
       </c>
       <c r="F29" s="20" t="s">
@@ -4216,7 +4292,7 @@
       <c r="D30" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="39" t="s">
         <v>65</v>
       </c>
       <c r="F30" s="20" t="s">
@@ -4242,7 +4318,7 @@
       <c r="D31" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="42" t="s">
+      <c r="E31" s="39" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="20" t="s">
@@ -4298,19 +4374,19 @@
     <row r="35" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="20"/>
       <c r="C35" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D35" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="42" t="s">
-        <v>80</v>
+      <c r="E35" s="39" t="s">
+        <v>75</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H35" s="22" t="s">
         <v>45</v>
@@ -4329,14 +4405,14 @@
       <c r="D36" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="42" t="s">
-        <v>79</v>
+      <c r="E36" s="39" t="s">
+        <v>74</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>46</v>
@@ -4355,14 +4431,14 @@
       <c r="D37" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="42" t="s">
-        <v>78</v>
+      <c r="E37" s="39" t="s">
+        <v>73</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>44</v>
@@ -4395,7 +4471,7 @@
       <c r="D39" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="E39" s="39" t="s">
         <v>61</v>
       </c>
       <c r="F39" s="20" t="s">
@@ -4421,7 +4497,7 @@
       <c r="D40" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="39" t="s">
         <v>62</v>
       </c>
       <c r="F40" s="20" t="s">
@@ -4447,7 +4523,7 @@
       <c r="D41" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="42" t="s">
+      <c r="E41" s="39" t="s">
         <v>63</v>
       </c>
       <c r="F41" s="20" t="s">
@@ -4475,19 +4551,19 @@
       <c r="C43" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="D43" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E43" s="47"/>
+      <c r="E43" s="42"/>
       <c r="F43" s="19"/>
-      <c r="G43" s="44"/>
+      <c r="G43" s="19"/>
       <c r="H43" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="J43" s="47"/>
+      <c r="J43" s="42"/>
     </row>
     <row r="44" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="17"/>
@@ -4501,10 +4577,10 @@
       <c r="F44" s="30"/>
       <c r="G44" s="30"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="49" t="s">
+      <c r="I44" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="J44" s="49"/>
+      <c r="J44" s="44"/>
     </row>
     <row r="45" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B45" s="18"/>
@@ -4518,8 +4594,8 @@
       <c r="F45" s="30"/>
       <c r="G45" s="30"/>
       <c r="H45" s="23"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:11" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -4552,7 +4628,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E49" s="33"/>
       <c r="I49" s="15"/>
@@ -4576,38 +4652,58 @@
     <mergeCell ref="D43:E43"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="C8:J9 C13:J14 C25:J27 C44:J45">
-    <cfRule type="expression" dxfId="4" priority="7">
+  <conditionalFormatting sqref="C9:J9 C14:J14 C25:F27 C44:J45 H25:J27 C13:F13 H13:J13 C8:F8 H8:J8">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:J19">
-    <cfRule type="expression" dxfId="3" priority="3">
+  <conditionalFormatting sqref="C19:J19 C18:F18 H18:J18">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:J31">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:J37">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:J41">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I39:J41 I18:J19 I35:J37 I29:J31 I25:J27 I8:J9 I13:J14">
-    <cfRule type="iconSet" priority="304">
+    <cfRule type="iconSet" priority="308">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
       </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G27">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/_Learn/Yi.Studio.event/latest.xlsx
+++ b/_Learn/Yi.Studio.event/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YiSolutions\_Learn\Yi.Studio.event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0FB26A-90DE-4D19-99B5-A0F2311A7EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71B1869-FF83-43E9-BB2E-95C5906C9E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1121,22 +1121,6 @@
 SHA-256</t>
   </si>
   <si>
-    <t>mul_Yi_Windows_11_24H2_With_Office_365_x64_2l1_19in1_x90ra8bv_january_2025.iso
-48D660147372C1E70722A716E99167F3CD9D6F2ABF6F3B65F35425586BFBCC39</t>
-  </si>
-  <si>
-    <t>mul_Yi_Windows_11_24H2_With_Office_2024_x64_2l1_19in1_80gscakk_january_2025.iso
-C7BD3EFF77EA01A29769CBC3892CF0016CD1A9BB8820BDD0E637CE0B905466BC</t>
-  </si>
-  <si>
-    <t>mul_Yi_Windows_11_24H2_x64_2l1_19in1_1y8zo69n_january_2025.iso
-E17F7740ABB0B69BC91C39E28B9B01310DB71C2B0294112690404F48421F9C4E</t>
-  </si>
-  <si>
-    <t>mul_Yi_Windows_11_24H2_x64_3l1_19in1_q3s8w5h5_january_2025.iso
-448150324F57EEBF7BA5EA38CFE7B8DA2D16005104BA8E994D87BC1BA22FD2F8</t>
-  </si>
-  <si>
     <t>mul_Yi_Windows_11_24H2_x64_5l1_19in1_tdskq49q_january_2025.iso
 CC2A15399A5560309A519B320645681D660254D66EED3917552A889B4B6B6CCA</t>
   </si>
@@ -1205,31 +1189,47 @@
 E453C0725D3F54901E0F86BE3A4A49E29954A49BD1E50AA8F5464D91B3FD9586</t>
   </si>
   <si>
-    <t>mul_Yi_Windows_11_24H2_x64_2l1_19in1_f2got7ei_november_2025.iso
+    <t xml:space="preserve">  Windows 11 25H2 26200.7296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2025 / 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Package event code: 25S4 ( 25 = 2025, S = quarter, 4 = Q4, N = November ), this system is packaged by Yi's Solutions v1.0.1.8 autopilot, go to learn or customize the package: https://fengyi.tel/solutions, https://github.com/ilikeyi/solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  封装事件代号：25S4N（ 25 = 2025 年、S = 季度，4 = 第 4 季度，N = 11 月 ），此系统由 Yi's Solutions v1.0.1.8 自动驾驶仪封装，前往学习或自定义封装：https://fengyi.tel/solutions，https://github.com/ilikeyi/solutions</t>
+  </si>
+  <si>
+    <t>25S4N</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_25H2_x64_2l1_19in1_z21q1n0v_november_2025.iso
+BB920DEE03E37691E90A868AE8CCE37E819785A127F1642461AEE7516A0A08AB</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_25H2_With_Office_2024_x64_2l1_19in1_2llm7ros_november_2025.iso
+EDA9F682E8EA562B0287DCDE2E3641796DA4752DAEBE2ED1DB85C6F5DC50D667</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_25H2_With_Office_365_x64_2l1_19in1_d0v9ezk4_november_2025.iso
+30EADA94D2C06E4E4E3A8D9B96BB1E389CCB7D82834365F76367CB60C8979B69</t>
+  </si>
+  <si>
+    <t>mul_Yi_Windows_11_25H2_x64_2l1_19in1_f2got7ei_november_2025.iso
 7C4DB229543BFA6BF3E65B1F29C2E8A85C1F2778827C55803221FDA39D45B474</t>
   </si>
   <si>
-    <t>mul_Yi_Windows_11_24H2_With_Office_2024_x64_2l1_19in1_05xisefy_november_2025.iso
+    <t>mul_Yi_Windows_11_25H2_With_Office_2024_x64_2l1_19in1_05xisefy_november_2025.iso
 0F9F945798CEBCAC70F8854D50E5B7333A8F72361B1E3C281D8732055428A079</t>
   </si>
   <si>
-    <t>mul_Yi_Windows_11_24H2_With_Office_365_x64_2l1_19in1_m3l7sjp7_november_2025.iso
+    <t>mul_Yi_Windows_11_25H2_With_Office_365_x64_2l1_19in1_m3l7sjp7_november_2025.iso
 1ED18D7ECF7BDB2C7D8E84FC6CC8502473AB8347335B6826A3B1AC502E9A8911</t>
   </si>
   <si>
-    <t xml:space="preserve">  Windows 11 25H2 26200.7296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2025 / 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Package event code: 25S4 ( 25 = 2025, S = quarter, 4 = Q4, N = November ), this system is packaged by Yi's Solutions v1.0.1.8 autopilot, go to learn or customize the package: https://fengyi.tel/solutions, https://github.com/ilikeyi/solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  封装事件代号：25S4N（ 25 = 2025 年、S = 季度，4 = 第 4 季度，N = 11 月 ），此系统由 Yi's Solutions v1.0.1.8 自动驾驶仪封装，前往学习或自定义封装：https://fengyi.tel/solutions，https://github.com/ilikeyi/solutions</t>
-  </si>
-  <si>
-    <t>25S4N</t>
+    <t>mul_Yi_Windows_11_25H2_x64_3l1_19in1_xsnqot4v_november_2025.iso
+2685706953BF773E3EAF59ED475DA6FFB1AE87FBBCCE441C97E3ADB9C3793578</t>
   </si>
 </sst>
 </file>
@@ -1699,46 +1699,7 @@
     <cellStyle name="Total" xfId="4" builtinId="25" customBuiltin="1"/>
     <cellStyle name="z Hidden Text" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill>
@@ -2058,17 +2019,17 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Home Inventory" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Home Inventory" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="27"/>
-      <tableStyleElement type="headerRow" dxfId="26"/>
-      <tableStyleElement type="totalRow" dxfId="25"/>
-      <tableStyleElement type="lastColumn" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
-      <tableStyleElement type="firstTotalCell" dxfId="21"/>
+      <tableStyleElement type="wholeTable" dxfId="24"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="totalRow" dxfId="22"/>
+      <tableStyleElement type="lastColumn" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
+      <tableStyleElement type="firstTotalCell" dxfId="18"/>
     </tableStyle>
     <tableStyle name="Home Inventory Slicer" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="20"/>
-      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2605,7 +2566,7 @@
     <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9"/>
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -2640,7 +2601,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H5" s="19" t="s">
         <v>27</v>
@@ -2679,19 +2640,19 @@
     <row r="8" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="20"/>
       <c r="C8" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D8" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>42</v>
@@ -2706,19 +2667,19 @@
     <row r="9" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D9" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>42</v>
@@ -2767,19 +2728,19 @@
     <row r="13" spans="1:11" s="15" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="20"/>
       <c r="C13" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>42</v>
@@ -2794,19 +2755,19 @@
     <row r="14" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D14" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>42</v>
@@ -2853,19 +2814,19 @@
     <row r="18" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="20"/>
       <c r="C18" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>42</v>
@@ -2880,19 +2841,19 @@
     <row r="19" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="20"/>
       <c r="C19" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>42</v>
@@ -2967,19 +2928,19 @@
     <row r="25" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>42</v>
@@ -2998,13 +2959,13 @@
         <v>52</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>43</v>
@@ -3023,13 +2984,13 @@
         <v>52</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>41</v>
@@ -3055,19 +3016,19 @@
     <row r="29" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="20"/>
       <c r="C29" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D29" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>42</v>
@@ -3087,13 +3048,13 @@
         <v>52</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>43</v>
@@ -3112,13 +3073,13 @@
         <v>52</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>41</v>
@@ -3165,19 +3126,19 @@
     <row r="35" spans="2:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="20"/>
       <c r="C35" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D35" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H35" s="22" t="s">
         <v>42</v>
@@ -3196,13 +3157,13 @@
         <v>52</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>43</v>
@@ -3221,13 +3182,13 @@
         <v>52</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>41</v>
@@ -3253,19 +3214,19 @@
     <row r="39" spans="2:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="20"/>
       <c r="C39" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>52</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H39" s="22" t="s">
         <v>42</v>
@@ -3284,13 +3245,13 @@
         <v>52</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>43</v>
@@ -3309,13 +3270,13 @@
         <v>52</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>41</v>
@@ -3410,7 +3371,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E49" s="33"/>
       <c r="I49" s="15"/>
@@ -3667,42 +3628,42 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:J9">
-    <cfRule type="expression" dxfId="18" priority="11">
+    <cfRule type="expression" dxfId="15" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:J14 C13:F13 H13:J13">
-    <cfRule type="expression" dxfId="17" priority="10">
+  <conditionalFormatting sqref="C13:J14">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:J19 C18:F18 H18:J18">
-    <cfRule type="expression" dxfId="16" priority="8">
+  <conditionalFormatting sqref="C18:J19">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:J27">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:J31">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="11" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:J37">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:J41">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:J45">
-    <cfRule type="expression" dxfId="11" priority="58">
+    <cfRule type="expression" dxfId="8" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3713,16 +3674,6 @@
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
       </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3796,7 +3747,7 @@
     <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9"/>
       <c r="C3" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -3832,7 +3783,7 @@
         <v>49</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H5" s="19" t="s">
         <v>26</v>
@@ -3873,19 +3824,19 @@
     <row r="8" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="20"/>
       <c r="C8" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D8" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>45</v>
@@ -3901,19 +3852,19 @@
     <row r="9" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D9" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>45</v>
@@ -3961,19 +3912,19 @@
     <row r="13" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="20"/>
       <c r="C13" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>45</v>
@@ -3989,19 +3940,19 @@
     <row r="14" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D14" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>45</v>
@@ -4049,19 +4000,19 @@
     <row r="18" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="20"/>
       <c r="C18" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>45</v>
@@ -4077,19 +4028,19 @@
     <row r="19" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="20"/>
       <c r="C19" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>45</v>
@@ -4169,19 +4120,19 @@
     <row r="25" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20"/>
       <c r="C25" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>45</v>
@@ -4201,13 +4152,13 @@
         <v>53</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>46</v>
@@ -4227,13 +4178,13 @@
         <v>53</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>44</v>
@@ -4261,19 +4212,19 @@
     <row r="29" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="20"/>
       <c r="C29" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D29" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H29" s="27" t="s">
         <v>45</v>
@@ -4293,13 +4244,13 @@
         <v>53</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>46</v>
@@ -4319,13 +4270,13 @@
         <v>53</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>44</v>
@@ -4374,19 +4325,19 @@
     <row r="35" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="20"/>
       <c r="C35" s="20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D35" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H35" s="22" t="s">
         <v>45</v>
@@ -4406,13 +4357,13 @@
         <v>53</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>46</v>
@@ -4432,13 +4383,13 @@
         <v>53</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>44</v>
@@ -4466,19 +4417,19 @@
     <row r="39" spans="1:11" ht="55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="20"/>
       <c r="C39" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>53</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H39" s="22" t="s">
         <v>45</v>
@@ -4498,13 +4449,13 @@
         <v>53</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>46</v>
@@ -4524,13 +4475,13 @@
         <v>53</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>50</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>44</v>
@@ -4628,7 +4579,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E49" s="33"/>
       <c r="I49" s="15"/>
@@ -4652,28 +4603,43 @@
     <mergeCell ref="D43:E43"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="C9:J9 C14:J14 C25:F27 C44:J45 H25:J27 C13:F13 H13:J13 C8:F8 H8:J8">
-    <cfRule type="expression" dxfId="10" priority="11">
+  <conditionalFormatting sqref="C8:J9">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:J19 C18:F18 H18:J18">
-    <cfRule type="expression" dxfId="9" priority="7">
+  <conditionalFormatting sqref="C13:J14">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:J19">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:J27">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:J31">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:J37">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C39:J41">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C44:J45">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4684,26 +4650,6 @@
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
       </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25:G27">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
